--- a/rcads/data/xls/10_Instruments.xlsx
+++ b/rcads/data/xls/10_Instruments.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_10_Instruments"/>
   </sheets>
   <definedNames>
-    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$J$177</definedName>
+    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$K$189</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:K189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -369,30 +369,35 @@
       </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
           <t>Informant</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>Authorized</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>ReadRighttoLeft</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>Unavailable(NotGenerated)</t>
         </is>
@@ -416,16 +421,19 @@
       <c r="E2" s="0">
         <v>1</v>
       </c>
-      <c r="G2" s="0" t="b">
-        <v>0</v>
+      <c r="F2" s="0">
+        <v>1</v>
       </c>
       <c r="H2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -445,18 +453,21 @@
         <v>1</v>
       </c>
       <c r="E3" s="0">
-        <v>2</v>
-      </c>
-      <c r="G3" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F3" s="0">
+        <v>2</v>
       </c>
       <c r="H3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -478,16 +489,19 @@
       <c r="E4" s="0">
         <v>1</v>
       </c>
-      <c r="G4" s="0" t="b">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>1</v>
       </c>
       <c r="H4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -507,18 +521,21 @@
         <v>1</v>
       </c>
       <c r="E5" s="0">
-        <v>2</v>
-      </c>
-      <c r="G5" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="0">
+        <v>2</v>
       </c>
       <c r="H5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -538,18 +555,21 @@
         <v>9</v>
       </c>
       <c r="E6" s="0">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F6" s="0">
+        <v>1</v>
       </c>
       <c r="H6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -569,18 +589,21 @@
         <v>9</v>
       </c>
       <c r="E7" s="0">
-        <v>2</v>
-      </c>
-      <c r="G7" s="0" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F7" s="0">
+        <v>2</v>
       </c>
       <c r="H7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -600,18 +623,21 @@
         <v>9</v>
       </c>
       <c r="E8" s="0">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F8" s="0">
+        <v>1</v>
       </c>
       <c r="H8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -631,18 +657,21 @@
         <v>9</v>
       </c>
       <c r="E9" s="0">
-        <v>2</v>
-      </c>
-      <c r="G9" s="0" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F9" s="0">
+        <v>2</v>
       </c>
       <c r="H9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -662,18 +691,21 @@
         <v>4</v>
       </c>
       <c r="E10" s="0">
-        <v>1</v>
-      </c>
-      <c r="G10" s="0" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F10" s="0">
+        <v>1</v>
       </c>
       <c r="H10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -695,16 +727,19 @@
       <c r="E11" s="0">
         <v>2</v>
       </c>
-      <c r="G11" s="0" t="b">
-        <v>0</v>
+      <c r="F11" s="0">
+        <v>2</v>
       </c>
       <c r="H11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -724,18 +759,21 @@
         <v>4</v>
       </c>
       <c r="E12" s="0">
-        <v>1</v>
-      </c>
-      <c r="G12" s="0" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1</v>
       </c>
       <c r="H12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -757,16 +795,19 @@
       <c r="E13" s="0">
         <v>2</v>
       </c>
-      <c r="G13" s="0" t="b">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>2</v>
       </c>
       <c r="H13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -786,15 +827,15 @@
         <v>8</v>
       </c>
       <c r="E14" s="0">
-        <v>1</v>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>OG Bouvard version</t>
-        </is>
-      </c>
-      <c r="G14" s="0" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F14" s="0">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>OG Bouvard version - has empirical study validating this version</t>
+        </is>
       </c>
       <c r="H14" s="0" t="b">
         <v>0</v>
@@ -803,6 +844,9 @@
         <v>0</v>
       </c>
       <c r="J14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -819,26 +863,29 @@
         <v>1</v>
       </c>
       <c r="D15" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E15" s="0">
-        <v>2</v>
-      </c>
-      <c r="F15" s="0" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F15" s="0">
+        <v>2</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>Chantal Caron et al 2018</t>
         </is>
       </c>
-      <c r="G15" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H15" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -858,16 +905,16 @@
         <v>8</v>
       </c>
       <c r="E16" s="0">
-        <v>1</v>
-      </c>
-      <c r="F16" s="0" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="F16" s="0">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>RCADS team generated</t>
         </is>
       </c>
-      <c r="G16" s="0" t="b">
-        <v>0</v>
-      </c>
       <c r="H16" s="0" t="b">
         <v>0</v>
       </c>
@@ -875,6 +922,9 @@
         <v>0</v>
       </c>
       <c r="J16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -894,23 +944,26 @@
         <v>8</v>
       </c>
       <c r="E17" s="0">
-        <v>2</v>
-      </c>
-      <c r="F17" s="0" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="F17" s="0">
+        <v>2</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>No items; Based on Boustani update of France French version</t>
         </is>
       </c>
-      <c r="G17" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H17" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -929,11 +982,8 @@
       <c r="D18" s="0">
         <v>21</v>
       </c>
-      <c r="E18" s="0">
-        <v>1</v>
-      </c>
-      <c r="G18" s="0" t="b">
-        <v>0</v>
+      <c r="F18" s="0">
+        <v>1</v>
       </c>
       <c r="H18" s="0" t="b">
         <v>0</v>
@@ -942,6 +992,9 @@
         <v>0</v>
       </c>
       <c r="J18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -960,11 +1013,8 @@
       <c r="D19" s="0">
         <v>21</v>
       </c>
-      <c r="E19" s="0">
-        <v>2</v>
-      </c>
-      <c r="G19" s="0" t="b">
-        <v>0</v>
+      <c r="F19" s="0">
+        <v>2</v>
       </c>
       <c r="H19" s="0" t="b">
         <v>0</v>
@@ -973,6 +1023,9 @@
         <v>0</v>
       </c>
       <c r="J19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -991,11 +1044,8 @@
       <c r="D20" s="0">
         <v>21</v>
       </c>
-      <c r="E20" s="0">
-        <v>1</v>
-      </c>
-      <c r="G20" s="0" t="b">
-        <v>0</v>
+      <c r="F20" s="0">
+        <v>1</v>
       </c>
       <c r="H20" s="0" t="b">
         <v>0</v>
@@ -1004,6 +1054,9 @@
         <v>0</v>
       </c>
       <c r="J20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1022,11 +1075,8 @@
       <c r="D21" s="0">
         <v>21</v>
       </c>
-      <c r="E21" s="0">
-        <v>2</v>
-      </c>
-      <c r="G21" s="0" t="b">
-        <v>0</v>
+      <c r="F21" s="0">
+        <v>2</v>
       </c>
       <c r="H21" s="0" t="b">
         <v>0</v>
@@ -1035,6 +1085,9 @@
         <v>0</v>
       </c>
       <c r="J21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1053,19 +1106,19 @@
       <c r="D22" s="0">
         <v>2</v>
       </c>
-      <c r="E22" s="0">
-        <v>1</v>
-      </c>
-      <c r="G22" s="0" t="b">
-        <v>0</v>
+      <c r="F22" s="0">
+        <v>1</v>
       </c>
       <c r="H22" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I22" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1084,19 +1137,19 @@
       <c r="D23" s="0">
         <v>2</v>
       </c>
-      <c r="E23" s="0">
-        <v>2</v>
-      </c>
-      <c r="G23" s="0" t="b">
-        <v>0</v>
+      <c r="F23" s="0">
+        <v>2</v>
       </c>
       <c r="H23" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1115,19 +1168,19 @@
       <c r="D24" s="0">
         <v>2</v>
       </c>
-      <c r="E24" s="0">
-        <v>1</v>
-      </c>
-      <c r="G24" s="0" t="b">
-        <v>0</v>
+      <c r="F24" s="0">
+        <v>1</v>
       </c>
       <c r="H24" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1146,19 +1199,19 @@
       <c r="D25" s="0">
         <v>2</v>
       </c>
-      <c r="E25" s="0">
-        <v>2</v>
-      </c>
-      <c r="G25" s="0" t="b">
-        <v>0</v>
+      <c r="F25" s="0">
+        <v>2</v>
       </c>
       <c r="H25" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I25" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1177,11 +1230,8 @@
       <c r="D26" s="0">
         <v>3</v>
       </c>
-      <c r="E26" s="0">
-        <v>1</v>
-      </c>
-      <c r="G26" s="0" t="b">
-        <v>0</v>
+      <c r="F26" s="0">
+        <v>1</v>
       </c>
       <c r="H26" s="0" t="b">
         <v>0</v>
@@ -1190,6 +1240,9 @@
         <v>0</v>
       </c>
       <c r="J26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1208,11 +1261,8 @@
       <c r="D27" s="0">
         <v>3</v>
       </c>
-      <c r="E27" s="0">
-        <v>2</v>
-      </c>
-      <c r="G27" s="0" t="b">
-        <v>0</v>
+      <c r="F27" s="0">
+        <v>2</v>
       </c>
       <c r="H27" s="0" t="b">
         <v>0</v>
@@ -1221,6 +1271,9 @@
         <v>0</v>
       </c>
       <c r="J27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1239,11 +1292,8 @@
       <c r="D28" s="0">
         <v>3</v>
       </c>
-      <c r="E28" s="0">
-        <v>1</v>
-      </c>
-      <c r="G28" s="0" t="b">
-        <v>0</v>
+      <c r="F28" s="0">
+        <v>1</v>
       </c>
       <c r="H28" s="0" t="b">
         <v>0</v>
@@ -1252,6 +1302,9 @@
         <v>0</v>
       </c>
       <c r="J28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1270,11 +1323,8 @@
       <c r="D29" s="0">
         <v>3</v>
       </c>
-      <c r="E29" s="0">
-        <v>2</v>
-      </c>
-      <c r="G29" s="0" t="b">
-        <v>0</v>
+      <c r="F29" s="0">
+        <v>2</v>
       </c>
       <c r="H29" s="0" t="b">
         <v>0</v>
@@ -1283,6 +1333,9 @@
         <v>0</v>
       </c>
       <c r="J29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1302,10 +1355,10 @@
         <v>5</v>
       </c>
       <c r="E30" s="0">
-        <v>1</v>
-      </c>
-      <c r="G30" s="0" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F30" s="0">
+        <v>1</v>
       </c>
       <c r="H30" s="0" t="b">
         <v>0</v>
@@ -1314,6 +1367,9 @@
         <v>0</v>
       </c>
       <c r="J30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1333,10 +1389,10 @@
         <v>5</v>
       </c>
       <c r="E31" s="0">
-        <v>2</v>
-      </c>
-      <c r="G31" s="0" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F31" s="0">
+        <v>2</v>
       </c>
       <c r="H31" s="0" t="b">
         <v>0</v>
@@ -1345,6 +1401,9 @@
         <v>0</v>
       </c>
       <c r="J31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1364,10 +1423,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="0">
-        <v>1</v>
-      </c>
-      <c r="G32" s="0" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F32" s="0">
+        <v>1</v>
       </c>
       <c r="H32" s="0" t="b">
         <v>0</v>
@@ -1376,6 +1435,9 @@
         <v>0</v>
       </c>
       <c r="J32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1395,10 +1457,10 @@
         <v>5</v>
       </c>
       <c r="E33" s="0">
-        <v>2</v>
-      </c>
-      <c r="G33" s="0" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F33" s="0">
+        <v>2</v>
       </c>
       <c r="H33" s="0" t="b">
         <v>0</v>
@@ -1407,6 +1469,9 @@
         <v>0</v>
       </c>
       <c r="J33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1425,11 +1490,8 @@
       <c r="D34" s="0">
         <v>6</v>
       </c>
-      <c r="E34" s="0">
-        <v>1</v>
-      </c>
-      <c r="G34" s="0" t="b">
-        <v>0</v>
+      <c r="F34" s="0">
+        <v>1</v>
       </c>
       <c r="H34" s="0" t="b">
         <v>0</v>
@@ -1438,6 +1500,9 @@
         <v>0</v>
       </c>
       <c r="J34" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1456,11 +1521,8 @@
       <c r="D35" s="0">
         <v>6</v>
       </c>
-      <c r="E35" s="0">
-        <v>2</v>
-      </c>
-      <c r="G35" s="0" t="b">
-        <v>0</v>
+      <c r="F35" s="0">
+        <v>2</v>
       </c>
       <c r="H35" s="0" t="b">
         <v>0</v>
@@ -1469,6 +1531,9 @@
         <v>0</v>
       </c>
       <c r="J35" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1487,11 +1552,8 @@
       <c r="D36" s="0">
         <v>6</v>
       </c>
-      <c r="E36" s="0">
-        <v>1</v>
-      </c>
-      <c r="G36" s="0" t="b">
-        <v>0</v>
+      <c r="F36" s="0">
+        <v>1</v>
       </c>
       <c r="H36" s="0" t="b">
         <v>0</v>
@@ -1500,6 +1562,9 @@
         <v>0</v>
       </c>
       <c r="J36" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1518,11 +1583,8 @@
       <c r="D37" s="0">
         <v>6</v>
       </c>
-      <c r="E37" s="0">
-        <v>2</v>
-      </c>
-      <c r="G37" s="0" t="b">
-        <v>0</v>
+      <c r="F37" s="0">
+        <v>2</v>
       </c>
       <c r="H37" s="0" t="b">
         <v>0</v>
@@ -1531,6 +1593,9 @@
         <v>0</v>
       </c>
       <c r="J37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1549,11 +1614,8 @@
       <c r="D38" s="0">
         <v>7</v>
       </c>
-      <c r="E38" s="0">
-        <v>1</v>
-      </c>
-      <c r="G38" s="0" t="b">
-        <v>0</v>
+      <c r="F38" s="0">
+        <v>1</v>
       </c>
       <c r="H38" s="0" t="b">
         <v>0</v>
@@ -1562,6 +1624,9 @@
         <v>0</v>
       </c>
       <c r="J38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1580,11 +1645,8 @@
       <c r="D39" s="0">
         <v>7</v>
       </c>
-      <c r="E39" s="0">
-        <v>2</v>
-      </c>
-      <c r="G39" s="0" t="b">
-        <v>0</v>
+      <c r="F39" s="0">
+        <v>2</v>
       </c>
       <c r="H39" s="0" t="b">
         <v>0</v>
@@ -1593,6 +1655,9 @@
         <v>0</v>
       </c>
       <c r="J39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1611,11 +1676,8 @@
       <c r="D40" s="0">
         <v>7</v>
       </c>
-      <c r="E40" s="0">
-        <v>1</v>
-      </c>
-      <c r="G40" s="0" t="b">
-        <v>0</v>
+      <c r="F40" s="0">
+        <v>1</v>
       </c>
       <c r="H40" s="0" t="b">
         <v>0</v>
@@ -1624,6 +1686,9 @@
         <v>0</v>
       </c>
       <c r="J40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1642,11 +1707,8 @@
       <c r="D41" s="0">
         <v>7</v>
       </c>
-      <c r="E41" s="0">
-        <v>2</v>
-      </c>
-      <c r="G41" s="0" t="b">
-        <v>0</v>
+      <c r="F41" s="0">
+        <v>2</v>
       </c>
       <c r="H41" s="0" t="b">
         <v>0</v>
@@ -1655,6 +1717,9 @@
         <v>0</v>
       </c>
       <c r="J41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1673,11 +1738,8 @@
       <c r="D42" s="0">
         <v>10</v>
       </c>
-      <c r="E42" s="0">
-        <v>1</v>
-      </c>
-      <c r="G42" s="0" t="b">
-        <v>0</v>
+      <c r="F42" s="0">
+        <v>1</v>
       </c>
       <c r="H42" s="0" t="b">
         <v>0</v>
@@ -1686,6 +1748,9 @@
         <v>0</v>
       </c>
       <c r="J42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1704,11 +1769,8 @@
       <c r="D43" s="0">
         <v>10</v>
       </c>
-      <c r="E43" s="0">
-        <v>2</v>
-      </c>
-      <c r="G43" s="0" t="b">
-        <v>0</v>
+      <c r="F43" s="0">
+        <v>2</v>
       </c>
       <c r="H43" s="0" t="b">
         <v>0</v>
@@ -1717,6 +1779,9 @@
         <v>0</v>
       </c>
       <c r="J43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1735,11 +1800,8 @@
       <c r="D44" s="0">
         <v>10</v>
       </c>
-      <c r="E44" s="0">
-        <v>1</v>
-      </c>
-      <c r="G44" s="0" t="b">
-        <v>0</v>
+      <c r="F44" s="0">
+        <v>1</v>
       </c>
       <c r="H44" s="0" t="b">
         <v>0</v>
@@ -1748,6 +1810,9 @@
         <v>0</v>
       </c>
       <c r="J44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1766,11 +1831,8 @@
       <c r="D45" s="0">
         <v>10</v>
       </c>
-      <c r="E45" s="0">
-        <v>2</v>
-      </c>
-      <c r="G45" s="0" t="b">
-        <v>0</v>
+      <c r="F45" s="0">
+        <v>2</v>
       </c>
       <c r="H45" s="0" t="b">
         <v>0</v>
@@ -1779,6 +1841,9 @@
         <v>0</v>
       </c>
       <c r="J45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1797,11 +1862,8 @@
       <c r="D46" s="0">
         <v>11</v>
       </c>
-      <c r="E46" s="0">
-        <v>1</v>
-      </c>
-      <c r="G46" s="0" t="b">
-        <v>0</v>
+      <c r="F46" s="0">
+        <v>1</v>
       </c>
       <c r="H46" s="0" t="b">
         <v>0</v>
@@ -1810,6 +1872,9 @@
         <v>0</v>
       </c>
       <c r="J46" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1828,11 +1893,8 @@
       <c r="D47" s="0">
         <v>11</v>
       </c>
-      <c r="E47" s="0">
-        <v>2</v>
-      </c>
-      <c r="G47" s="0" t="b">
-        <v>0</v>
+      <c r="F47" s="0">
+        <v>2</v>
       </c>
       <c r="H47" s="0" t="b">
         <v>0</v>
@@ -1841,6 +1903,9 @@
         <v>0</v>
       </c>
       <c r="J47" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1859,11 +1924,8 @@
       <c r="D48" s="0">
         <v>11</v>
       </c>
-      <c r="E48" s="0">
-        <v>1</v>
-      </c>
-      <c r="G48" s="0" t="b">
-        <v>0</v>
+      <c r="F48" s="0">
+        <v>1</v>
       </c>
       <c r="H48" s="0" t="b">
         <v>0</v>
@@ -1872,6 +1934,9 @@
         <v>0</v>
       </c>
       <c r="J48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1890,11 +1955,8 @@
       <c r="D49" s="0">
         <v>11</v>
       </c>
-      <c r="E49" s="0">
-        <v>2</v>
-      </c>
-      <c r="G49" s="0" t="b">
-        <v>0</v>
+      <c r="F49" s="0">
+        <v>2</v>
       </c>
       <c r="H49" s="0" t="b">
         <v>0</v>
@@ -1903,6 +1965,9 @@
         <v>0</v>
       </c>
       <c r="J49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1921,11 +1986,8 @@
       <c r="D50" s="0">
         <v>12</v>
       </c>
-      <c r="E50" s="0">
-        <v>1</v>
-      </c>
-      <c r="G50" s="0" t="b">
-        <v>0</v>
+      <c r="F50" s="0">
+        <v>1</v>
       </c>
       <c r="H50" s="0" t="b">
         <v>0</v>
@@ -1934,6 +1996,9 @@
         <v>0</v>
       </c>
       <c r="J50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1952,11 +2017,8 @@
       <c r="D51" s="0">
         <v>12</v>
       </c>
-      <c r="E51" s="0">
-        <v>2</v>
-      </c>
-      <c r="G51" s="0" t="b">
-        <v>0</v>
+      <c r="F51" s="0">
+        <v>2</v>
       </c>
       <c r="H51" s="0" t="b">
         <v>0</v>
@@ -1965,6 +2027,9 @@
         <v>0</v>
       </c>
       <c r="J51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1983,11 +2048,8 @@
       <c r="D52" s="0">
         <v>12</v>
       </c>
-      <c r="E52" s="0">
-        <v>1</v>
-      </c>
-      <c r="G52" s="0" t="b">
-        <v>0</v>
+      <c r="F52" s="0">
+        <v>1</v>
       </c>
       <c r="H52" s="0" t="b">
         <v>0</v>
@@ -1996,6 +2058,9 @@
         <v>0</v>
       </c>
       <c r="J52" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2014,11 +2079,8 @@
       <c r="D53" s="0">
         <v>12</v>
       </c>
-      <c r="E53" s="0">
-        <v>2</v>
-      </c>
-      <c r="G53" s="0" t="b">
-        <v>0</v>
+      <c r="F53" s="0">
+        <v>2</v>
       </c>
       <c r="H53" s="0" t="b">
         <v>0</v>
@@ -2027,6 +2089,9 @@
         <v>0</v>
       </c>
       <c r="J53" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2045,11 +2110,8 @@
       <c r="D54" s="0">
         <v>13</v>
       </c>
-      <c r="E54" s="0">
-        <v>1</v>
-      </c>
-      <c r="G54" s="0" t="b">
-        <v>0</v>
+      <c r="F54" s="0">
+        <v>1</v>
       </c>
       <c r="H54" s="0" t="b">
         <v>0</v>
@@ -2058,6 +2120,9 @@
         <v>0</v>
       </c>
       <c r="J54" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2076,11 +2141,8 @@
       <c r="D55" s="0">
         <v>13</v>
       </c>
-      <c r="E55" s="0">
-        <v>2</v>
-      </c>
-      <c r="G55" s="0" t="b">
-        <v>0</v>
+      <c r="F55" s="0">
+        <v>2</v>
       </c>
       <c r="H55" s="0" t="b">
         <v>0</v>
@@ -2089,6 +2151,9 @@
         <v>0</v>
       </c>
       <c r="J55" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2107,11 +2172,8 @@
       <c r="D56" s="0">
         <v>13</v>
       </c>
-      <c r="E56" s="0">
-        <v>1</v>
-      </c>
-      <c r="G56" s="0" t="b">
-        <v>0</v>
+      <c r="F56" s="0">
+        <v>1</v>
       </c>
       <c r="H56" s="0" t="b">
         <v>0</v>
@@ -2120,6 +2182,9 @@
         <v>0</v>
       </c>
       <c r="J56" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2138,11 +2203,8 @@
       <c r="D57" s="0">
         <v>13</v>
       </c>
-      <c r="E57" s="0">
-        <v>2</v>
-      </c>
-      <c r="G57" s="0" t="b">
-        <v>0</v>
+      <c r="F57" s="0">
+        <v>2</v>
       </c>
       <c r="H57" s="0" t="b">
         <v>0</v>
@@ -2151,6 +2213,9 @@
         <v>0</v>
       </c>
       <c r="J57" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2169,11 +2234,8 @@
       <c r="D58" s="0">
         <v>14</v>
       </c>
-      <c r="E58" s="0">
-        <v>1</v>
-      </c>
-      <c r="G58" s="0" t="b">
-        <v>0</v>
+      <c r="F58" s="0">
+        <v>1</v>
       </c>
       <c r="H58" s="0" t="b">
         <v>0</v>
@@ -2182,6 +2244,9 @@
         <v>0</v>
       </c>
       <c r="J58" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2200,11 +2265,8 @@
       <c r="D59" s="0">
         <v>14</v>
       </c>
-      <c r="E59" s="0">
-        <v>2</v>
-      </c>
-      <c r="G59" s="0" t="b">
-        <v>0</v>
+      <c r="F59" s="0">
+        <v>2</v>
       </c>
       <c r="H59" s="0" t="b">
         <v>0</v>
@@ -2213,6 +2275,9 @@
         <v>0</v>
       </c>
       <c r="J59" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2231,11 +2296,8 @@
       <c r="D60" s="0">
         <v>14</v>
       </c>
-      <c r="E60" s="0">
-        <v>1</v>
-      </c>
-      <c r="G60" s="0" t="b">
-        <v>0</v>
+      <c r="F60" s="0">
+        <v>1</v>
       </c>
       <c r="H60" s="0" t="b">
         <v>0</v>
@@ -2244,6 +2306,9 @@
         <v>0</v>
       </c>
       <c r="J60" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2262,11 +2327,8 @@
       <c r="D61" s="0">
         <v>14</v>
       </c>
-      <c r="E61" s="0">
-        <v>2</v>
-      </c>
-      <c r="G61" s="0" t="b">
-        <v>0</v>
+      <c r="F61" s="0">
+        <v>2</v>
       </c>
       <c r="H61" s="0" t="b">
         <v>0</v>
@@ -2275,6 +2337,9 @@
         <v>0</v>
       </c>
       <c r="J61" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2293,11 +2358,8 @@
       <c r="D62" s="0">
         <v>15</v>
       </c>
-      <c r="E62" s="0">
-        <v>1</v>
-      </c>
-      <c r="G62" s="0" t="b">
-        <v>0</v>
+      <c r="F62" s="0">
+        <v>1</v>
       </c>
       <c r="H62" s="0" t="b">
         <v>0</v>
@@ -2306,6 +2368,9 @@
         <v>0</v>
       </c>
       <c r="J62" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2324,24 +2389,24 @@
       <c r="D63" s="0">
         <v>15</v>
       </c>
-      <c r="E63" s="0">
-        <v>2</v>
-      </c>
-      <c r="F63" s="0" t="inlineStr">
+      <c r="F63" s="0">
+        <v>2</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G63" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H63" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J63" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2360,11 +2425,8 @@
       <c r="D64" s="0">
         <v>15</v>
       </c>
-      <c r="E64" s="0">
-        <v>1</v>
-      </c>
-      <c r="G64" s="0" t="b">
-        <v>0</v>
+      <c r="F64" s="0">
+        <v>1</v>
       </c>
       <c r="H64" s="0" t="b">
         <v>0</v>
@@ -2373,6 +2435,9 @@
         <v>0</v>
       </c>
       <c r="J64" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2391,24 +2456,24 @@
       <c r="D65" s="0">
         <v>15</v>
       </c>
-      <c r="E65" s="0">
-        <v>2</v>
-      </c>
-      <c r="F65" s="0" t="inlineStr">
+      <c r="F65" s="0">
+        <v>2</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G65" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H65" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J65" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2427,11 +2492,8 @@
       <c r="D66" s="0">
         <v>16</v>
       </c>
-      <c r="E66" s="0">
-        <v>1</v>
-      </c>
-      <c r="G66" s="0" t="b">
-        <v>0</v>
+      <c r="F66" s="0">
+        <v>1</v>
       </c>
       <c r="H66" s="0" t="b">
         <v>0</v>
@@ -2440,6 +2502,9 @@
         <v>0</v>
       </c>
       <c r="J66" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2458,11 +2523,8 @@
       <c r="D67" s="0">
         <v>16</v>
       </c>
-      <c r="E67" s="0">
-        <v>2</v>
-      </c>
-      <c r="G67" s="0" t="b">
-        <v>0</v>
+      <c r="F67" s="0">
+        <v>2</v>
       </c>
       <c r="H67" s="0" t="b">
         <v>0</v>
@@ -2471,6 +2533,9 @@
         <v>0</v>
       </c>
       <c r="J67" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2489,11 +2554,8 @@
       <c r="D68" s="0">
         <v>16</v>
       </c>
-      <c r="E68" s="0">
-        <v>1</v>
-      </c>
-      <c r="G68" s="0" t="b">
-        <v>0</v>
+      <c r="F68" s="0">
+        <v>1</v>
       </c>
       <c r="H68" s="0" t="b">
         <v>0</v>
@@ -2502,6 +2564,9 @@
         <v>0</v>
       </c>
       <c r="J68" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2520,11 +2585,8 @@
       <c r="D69" s="0">
         <v>16</v>
       </c>
-      <c r="E69" s="0">
-        <v>2</v>
-      </c>
-      <c r="G69" s="0" t="b">
-        <v>0</v>
+      <c r="F69" s="0">
+        <v>2</v>
       </c>
       <c r="H69" s="0" t="b">
         <v>0</v>
@@ -2533,6 +2595,9 @@
         <v>0</v>
       </c>
       <c r="J69" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2551,11 +2616,8 @@
       <c r="D70" s="0">
         <v>17</v>
       </c>
-      <c r="E70" s="0">
-        <v>1</v>
-      </c>
-      <c r="G70" s="0" t="b">
-        <v>0</v>
+      <c r="F70" s="0">
+        <v>1</v>
       </c>
       <c r="H70" s="0" t="b">
         <v>0</v>
@@ -2564,6 +2626,9 @@
         <v>0</v>
       </c>
       <c r="J70" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2582,11 +2647,8 @@
       <c r="D71" s="0">
         <v>17</v>
       </c>
-      <c r="E71" s="0">
-        <v>2</v>
-      </c>
-      <c r="G71" s="0" t="b">
-        <v>0</v>
+      <c r="F71" s="0">
+        <v>2</v>
       </c>
       <c r="H71" s="0" t="b">
         <v>0</v>
@@ -2595,6 +2657,9 @@
         <v>0</v>
       </c>
       <c r="J71" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2613,11 +2678,8 @@
       <c r="D72" s="0">
         <v>17</v>
       </c>
-      <c r="E72" s="0">
-        <v>1</v>
-      </c>
-      <c r="G72" s="0" t="b">
-        <v>0</v>
+      <c r="F72" s="0">
+        <v>1</v>
       </c>
       <c r="H72" s="0" t="b">
         <v>0</v>
@@ -2626,6 +2688,9 @@
         <v>0</v>
       </c>
       <c r="J72" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2644,11 +2709,8 @@
       <c r="D73" s="0">
         <v>17</v>
       </c>
-      <c r="E73" s="0">
-        <v>2</v>
-      </c>
-      <c r="G73" s="0" t="b">
-        <v>0</v>
+      <c r="F73" s="0">
+        <v>2</v>
       </c>
       <c r="H73" s="0" t="b">
         <v>0</v>
@@ -2657,6 +2719,9 @@
         <v>0</v>
       </c>
       <c r="J73" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2675,11 +2740,8 @@
       <c r="D74" s="0">
         <v>18</v>
       </c>
-      <c r="E74" s="0">
-        <v>1</v>
-      </c>
-      <c r="G74" s="0" t="b">
-        <v>0</v>
+      <c r="F74" s="0">
+        <v>1</v>
       </c>
       <c r="H74" s="0" t="b">
         <v>0</v>
@@ -2688,6 +2750,9 @@
         <v>0</v>
       </c>
       <c r="J74" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2706,11 +2771,8 @@
       <c r="D75" s="0">
         <v>18</v>
       </c>
-      <c r="E75" s="0">
-        <v>2</v>
-      </c>
-      <c r="G75" s="0" t="b">
-        <v>0</v>
+      <c r="F75" s="0">
+        <v>2</v>
       </c>
       <c r="H75" s="0" t="b">
         <v>0</v>
@@ -2719,6 +2781,9 @@
         <v>0</v>
       </c>
       <c r="J75" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2737,11 +2802,8 @@
       <c r="D76" s="0">
         <v>18</v>
       </c>
-      <c r="E76" s="0">
-        <v>1</v>
-      </c>
-      <c r="G76" s="0" t="b">
-        <v>0</v>
+      <c r="F76" s="0">
+        <v>1</v>
       </c>
       <c r="H76" s="0" t="b">
         <v>0</v>
@@ -2750,6 +2812,9 @@
         <v>0</v>
       </c>
       <c r="J76" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2768,11 +2833,8 @@
       <c r="D77" s="0">
         <v>18</v>
       </c>
-      <c r="E77" s="0">
-        <v>2</v>
-      </c>
-      <c r="G77" s="0" t="b">
-        <v>0</v>
+      <c r="F77" s="0">
+        <v>2</v>
       </c>
       <c r="H77" s="0" t="b">
         <v>0</v>
@@ -2781,6 +2843,9 @@
         <v>0</v>
       </c>
       <c r="J77" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2800,10 +2865,10 @@
         <v>19</v>
       </c>
       <c r="E78" s="0">
-        <v>1</v>
-      </c>
-      <c r="G78" s="0" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="F78" s="0">
+        <v>1</v>
       </c>
       <c r="H78" s="0" t="b">
         <v>0</v>
@@ -2812,6 +2877,9 @@
         <v>0</v>
       </c>
       <c r="J78" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2830,24 +2898,24 @@
       <c r="D79" s="0">
         <v>19</v>
       </c>
-      <c r="E79" s="0">
-        <v>2</v>
-      </c>
-      <c r="F79" s="0" t="inlineStr">
+      <c r="F79" s="0">
+        <v>2</v>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G79" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H79" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J79" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2867,10 +2935,10 @@
         <v>19</v>
       </c>
       <c r="E80" s="0">
-        <v>1</v>
-      </c>
-      <c r="G80" s="0" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="F80" s="0">
+        <v>1</v>
       </c>
       <c r="H80" s="0" t="b">
         <v>0</v>
@@ -2879,6 +2947,9 @@
         <v>0</v>
       </c>
       <c r="J80" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2897,24 +2968,24 @@
       <c r="D81" s="0">
         <v>19</v>
       </c>
-      <c r="E81" s="0">
-        <v>2</v>
-      </c>
-      <c r="F81" s="0" t="inlineStr">
+      <c r="F81" s="0">
+        <v>2</v>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G81" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H81" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J81" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2933,11 +3004,8 @@
       <c r="D82" s="0">
         <v>20</v>
       </c>
-      <c r="E82" s="0">
-        <v>1</v>
-      </c>
-      <c r="G82" s="0" t="b">
-        <v>0</v>
+      <c r="F82" s="0">
+        <v>1</v>
       </c>
       <c r="H82" s="0" t="b">
         <v>0</v>
@@ -2946,6 +3014,9 @@
         <v>0</v>
       </c>
       <c r="J82" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2964,11 +3035,8 @@
       <c r="D83" s="0">
         <v>20</v>
       </c>
-      <c r="E83" s="0">
-        <v>2</v>
-      </c>
-      <c r="G83" s="0" t="b">
-        <v>0</v>
+      <c r="F83" s="0">
+        <v>2</v>
       </c>
       <c r="H83" s="0" t="b">
         <v>0</v>
@@ -2977,6 +3045,9 @@
         <v>0</v>
       </c>
       <c r="J83" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2995,11 +3066,8 @@
       <c r="D84" s="0">
         <v>20</v>
       </c>
-      <c r="E84" s="0">
-        <v>1</v>
-      </c>
-      <c r="G84" s="0" t="b">
-        <v>0</v>
+      <c r="F84" s="0">
+        <v>1</v>
       </c>
       <c r="H84" s="0" t="b">
         <v>0</v>
@@ -3008,6 +3076,9 @@
         <v>0</v>
       </c>
       <c r="J84" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3026,11 +3097,8 @@
       <c r="D85" s="0">
         <v>20</v>
       </c>
-      <c r="E85" s="0">
-        <v>2</v>
-      </c>
-      <c r="G85" s="0" t="b">
-        <v>0</v>
+      <c r="F85" s="0">
+        <v>2</v>
       </c>
       <c r="H85" s="0" t="b">
         <v>0</v>
@@ -3039,6 +3107,9 @@
         <v>0</v>
       </c>
       <c r="J85" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3057,11 +3128,8 @@
       <c r="D86" s="0">
         <v>22</v>
       </c>
-      <c r="E86" s="0">
-        <v>1</v>
-      </c>
-      <c r="G86" s="0" t="b">
-        <v>0</v>
+      <c r="F86" s="0">
+        <v>1</v>
       </c>
       <c r="H86" s="0" t="b">
         <v>0</v>
@@ -3070,6 +3138,9 @@
         <v>0</v>
       </c>
       <c r="J86" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3088,11 +3159,8 @@
       <c r="D87" s="0">
         <v>22</v>
       </c>
-      <c r="E87" s="0">
-        <v>2</v>
-      </c>
-      <c r="G87" s="0" t="b">
-        <v>0</v>
+      <c r="F87" s="0">
+        <v>2</v>
       </c>
       <c r="H87" s="0" t="b">
         <v>0</v>
@@ -3101,6 +3169,9 @@
         <v>0</v>
       </c>
       <c r="J87" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3119,11 +3190,8 @@
       <c r="D88" s="0">
         <v>22</v>
       </c>
-      <c r="E88" s="0">
-        <v>1</v>
-      </c>
-      <c r="G88" s="0" t="b">
-        <v>0</v>
+      <c r="F88" s="0">
+        <v>1</v>
       </c>
       <c r="H88" s="0" t="b">
         <v>0</v>
@@ -3132,6 +3200,9 @@
         <v>0</v>
       </c>
       <c r="J88" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3150,11 +3221,8 @@
       <c r="D89" s="0">
         <v>22</v>
       </c>
-      <c r="E89" s="0">
-        <v>2</v>
-      </c>
-      <c r="G89" s="0" t="b">
-        <v>0</v>
+      <c r="F89" s="0">
+        <v>2</v>
       </c>
       <c r="H89" s="0" t="b">
         <v>0</v>
@@ -3163,6 +3231,9 @@
         <v>0</v>
       </c>
       <c r="J89" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3181,11 +3252,8 @@
       <c r="D90" s="0">
         <v>23</v>
       </c>
-      <c r="E90" s="0">
-        <v>1</v>
-      </c>
-      <c r="G90" s="0" t="b">
-        <v>0</v>
+      <c r="F90" s="0">
+        <v>1</v>
       </c>
       <c r="H90" s="0" t="b">
         <v>0</v>
@@ -3194,6 +3262,9 @@
         <v>0</v>
       </c>
       <c r="J90" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3212,11 +3283,8 @@
       <c r="D91" s="0">
         <v>23</v>
       </c>
-      <c r="E91" s="0">
-        <v>2</v>
-      </c>
-      <c r="G91" s="0" t="b">
-        <v>0</v>
+      <c r="F91" s="0">
+        <v>2</v>
       </c>
       <c r="H91" s="0" t="b">
         <v>0</v>
@@ -3225,6 +3293,9 @@
         <v>0</v>
       </c>
       <c r="J91" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3243,11 +3314,8 @@
       <c r="D92" s="0">
         <v>23</v>
       </c>
-      <c r="E92" s="0">
-        <v>1</v>
-      </c>
-      <c r="G92" s="0" t="b">
-        <v>0</v>
+      <c r="F92" s="0">
+        <v>1</v>
       </c>
       <c r="H92" s="0" t="b">
         <v>0</v>
@@ -3256,6 +3324,9 @@
         <v>0</v>
       </c>
       <c r="J92" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3274,11 +3345,8 @@
       <c r="D93" s="0">
         <v>23</v>
       </c>
-      <c r="E93" s="0">
-        <v>2</v>
-      </c>
-      <c r="G93" s="0" t="b">
-        <v>0</v>
+      <c r="F93" s="0">
+        <v>2</v>
       </c>
       <c r="H93" s="0" t="b">
         <v>0</v>
@@ -3287,6 +3355,9 @@
         <v>0</v>
       </c>
       <c r="J93" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3305,24 +3376,24 @@
       <c r="D94" s="0">
         <v>24</v>
       </c>
-      <c r="E94" s="0">
-        <v>1</v>
-      </c>
-      <c r="F94" s="0" t="inlineStr">
+      <c r="F94" s="0">
+        <v>1</v>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
         <is>
           <t>incorrect item numbering after 29, missing item stem concept for item 35</t>
         </is>
       </c>
-      <c r="G94" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H94" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J94" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3341,11 +3412,8 @@
       <c r="D95" s="0">
         <v>24</v>
       </c>
-      <c r="E95" s="0">
-        <v>2</v>
-      </c>
-      <c r="G95" s="0" t="b">
-        <v>0</v>
+      <c r="F95" s="0">
+        <v>2</v>
       </c>
       <c r="H95" s="0" t="b">
         <v>0</v>
@@ -3354,6 +3422,9 @@
         <v>0</v>
       </c>
       <c r="J95" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3372,11 +3443,8 @@
       <c r="D96" s="0">
         <v>24</v>
       </c>
-      <c r="E96" s="0">
-        <v>1</v>
-      </c>
-      <c r="G96" s="0" t="b">
-        <v>0</v>
+      <c r="F96" s="0">
+        <v>1</v>
       </c>
       <c r="H96" s="0" t="b">
         <v>0</v>
@@ -3385,6 +3453,9 @@
         <v>0</v>
       </c>
       <c r="J96" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3403,11 +3474,8 @@
       <c r="D97" s="0">
         <v>24</v>
       </c>
-      <c r="E97" s="0">
-        <v>2</v>
-      </c>
-      <c r="G97" s="0" t="b">
-        <v>0</v>
+      <c r="F97" s="0">
+        <v>2</v>
       </c>
       <c r="H97" s="0" t="b">
         <v>0</v>
@@ -3416,6 +3484,9 @@
         <v>0</v>
       </c>
       <c r="J97" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3434,11 +3505,8 @@
       <c r="D98" s="0">
         <v>1</v>
       </c>
-      <c r="E98" s="0">
-        <v>1</v>
-      </c>
-      <c r="G98" s="0" t="b">
-        <v>0</v>
+      <c r="F98" s="0">
+        <v>1</v>
       </c>
       <c r="H98" s="0" t="b">
         <v>0</v>
@@ -3447,6 +3515,9 @@
         <v>0</v>
       </c>
       <c r="J98" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3465,11 +3536,8 @@
       <c r="D99" s="0">
         <v>1</v>
       </c>
-      <c r="E99" s="0">
-        <v>2</v>
-      </c>
-      <c r="G99" s="0" t="b">
-        <v>0</v>
+      <c r="F99" s="0">
+        <v>2</v>
       </c>
       <c r="H99" s="0" t="b">
         <v>0</v>
@@ -3478,6 +3546,9 @@
         <v>0</v>
       </c>
       <c r="J99" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3496,11 +3567,8 @@
       <c r="D100" s="0">
         <v>21</v>
       </c>
-      <c r="E100" s="0">
-        <v>1</v>
-      </c>
-      <c r="G100" s="0" t="b">
-        <v>0</v>
+      <c r="F100" s="0">
+        <v>1</v>
       </c>
       <c r="H100" s="0" t="b">
         <v>0</v>
@@ -3509,6 +3577,9 @@
         <v>0</v>
       </c>
       <c r="J100" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3527,11 +3598,8 @@
       <c r="D101" s="0">
         <v>21</v>
       </c>
-      <c r="E101" s="0">
-        <v>2</v>
-      </c>
-      <c r="G101" s="0" t="b">
-        <v>0</v>
+      <c r="F101" s="0">
+        <v>2</v>
       </c>
       <c r="H101" s="0" t="b">
         <v>0</v>
@@ -3540,6 +3608,9 @@
         <v>0</v>
       </c>
       <c r="J101" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3558,11 +3629,8 @@
       <c r="D102" s="0">
         <v>1</v>
       </c>
-      <c r="E102" s="0">
-        <v>1</v>
-      </c>
-      <c r="G102" s="0" t="b">
-        <v>0</v>
+      <c r="F102" s="0">
+        <v>1</v>
       </c>
       <c r="H102" s="0" t="b">
         <v>0</v>
@@ -3571,6 +3639,9 @@
         <v>0</v>
       </c>
       <c r="J102" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3589,11 +3660,8 @@
       <c r="D103" s="0">
         <v>1</v>
       </c>
-      <c r="E103" s="0">
-        <v>2</v>
-      </c>
-      <c r="G103" s="0" t="b">
-        <v>0</v>
+      <c r="F103" s="0">
+        <v>2</v>
       </c>
       <c r="H103" s="0" t="b">
         <v>0</v>
@@ -3602,6 +3670,9 @@
         <v>0</v>
       </c>
       <c r="J103" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3620,24 +3691,24 @@
       <c r="D104" s="0">
         <v>21</v>
       </c>
-      <c r="E104" s="0">
-        <v>1</v>
-      </c>
-      <c r="F104" s="0" t="inlineStr">
+      <c r="F104" s="0">
+        <v>1</v>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G104" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H104" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J104" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3656,24 +3727,24 @@
       <c r="D105" s="0">
         <v>21</v>
       </c>
-      <c r="E105" s="0">
-        <v>2</v>
-      </c>
-      <c r="F105" s="0" t="inlineStr">
+      <c r="F105" s="0">
+        <v>2</v>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G105" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H105" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J105" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3692,17 +3763,14 @@
       <c r="D106" s="0">
         <v>1</v>
       </c>
-      <c r="E106" s="0">
-        <v>2</v>
-      </c>
-      <c r="F106" s="0" t="inlineStr">
+      <c r="F106" s="0">
+        <v>2</v>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
         <is>
           <t>For autism eary intervention context</t>
         </is>
       </c>
-      <c r="G106" s="0" t="b">
-        <v>0</v>
-      </c>
       <c r="H106" s="0" t="b">
         <v>0</v>
       </c>
@@ -3710,6 +3778,9 @@
         <v>0</v>
       </c>
       <c r="J106" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3719,7 +3790,7 @@
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>PHQ-9-A-EN</t>
+          <t>PHQ-9-A-EN-UK</t>
         </is>
       </c>
       <c r="C107" s="0">
@@ -3729,11 +3800,11 @@
         <v>1</v>
       </c>
       <c r="E107" s="0">
+        <v>9</v>
+      </c>
+      <c r="F107" s="0">
         <v>4</v>
       </c>
-      <c r="G107" s="0" t="b">
-        <v>0</v>
-      </c>
       <c r="H107" s="0" t="b">
         <v>0</v>
       </c>
@@ -3741,6 +3812,9 @@
         <v>0</v>
       </c>
       <c r="J107" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3759,24 +3833,24 @@
       <c r="D108" s="0">
         <v>1</v>
       </c>
-      <c r="E108" s="0">
-        <v>1</v>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
+      <c r="F108" s="0">
+        <v>1</v>
+      </c>
+      <c r="G108" s="0" t="inlineStr">
         <is>
           <t>Manasi Kumar MMA derivative</t>
         </is>
       </c>
-      <c r="G108" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H108" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J108" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3795,24 +3869,24 @@
       <c r="D109" s="0">
         <v>26</v>
       </c>
-      <c r="E109" s="0">
-        <v>1</v>
-      </c>
-      <c r="F109" s="0" t="inlineStr">
+      <c r="F109" s="0">
+        <v>1</v>
+      </c>
+      <c r="G109" s="0" t="inlineStr">
         <is>
           <t>Manasi Kumar MMA derivative 2</t>
         </is>
       </c>
-      <c r="G109" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H109" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J109" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K109" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3831,11 +3905,8 @@
       <c r="D110" s="0">
         <v>27</v>
       </c>
-      <c r="E110" s="0">
-        <v>1</v>
-      </c>
-      <c r="G110" s="0" t="b">
-        <v>0</v>
+      <c r="F110" s="0">
+        <v>1</v>
       </c>
       <c r="H110" s="0" t="b">
         <v>0</v>
@@ -3844,6 +3915,9 @@
         <v>0</v>
       </c>
       <c r="J110" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3862,11 +3936,8 @@
       <c r="D111" s="0">
         <v>27</v>
       </c>
-      <c r="E111" s="0">
-        <v>2</v>
-      </c>
-      <c r="G111" s="0" t="b">
-        <v>0</v>
+      <c r="F111" s="0">
+        <v>2</v>
       </c>
       <c r="H111" s="0" t="b">
         <v>0</v>
@@ -3875,6 +3946,9 @@
         <v>0</v>
       </c>
       <c r="J111" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K111" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3893,11 +3967,8 @@
       <c r="D112" s="0">
         <v>13</v>
       </c>
-      <c r="E112" s="0">
-        <v>1</v>
-      </c>
-      <c r="G112" s="0" t="b">
-        <v>0</v>
+      <c r="F112" s="0">
+        <v>1</v>
       </c>
       <c r="H112" s="0" t="b">
         <v>0</v>
@@ -3906,6 +3977,9 @@
         <v>0</v>
       </c>
       <c r="J112" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K112" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3924,11 +3998,8 @@
       <c r="D113" s="0">
         <v>13</v>
       </c>
-      <c r="E113" s="0">
-        <v>2</v>
-      </c>
-      <c r="G113" s="0" t="b">
-        <v>0</v>
+      <c r="F113" s="0">
+        <v>2</v>
       </c>
       <c r="H113" s="0" t="b">
         <v>0</v>
@@ -3937,6 +4008,9 @@
         <v>0</v>
       </c>
       <c r="J113" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K113" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3955,24 +4029,24 @@
       <c r="D114" s="0">
         <v>8</v>
       </c>
-      <c r="E114" s="0">
-        <v>1</v>
-      </c>
-      <c r="F114" s="0" t="inlineStr">
+      <c r="F114" s="0">
+        <v>1</v>
+      </c>
+      <c r="G114" s="0" t="inlineStr">
         <is>
           <t>Boustani update</t>
         </is>
       </c>
-      <c r="G114" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H114" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J114" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3991,24 +4065,24 @@
       <c r="D115" s="0">
         <v>16</v>
       </c>
-      <c r="E115" s="0">
-        <v>1</v>
-      </c>
-      <c r="F115" s="0" t="inlineStr">
+      <c r="F115" s="0">
+        <v>1</v>
+      </c>
+      <c r="G115" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G115" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H115" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J115" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K115" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4027,24 +4101,24 @@
       <c r="D116" s="0">
         <v>16</v>
       </c>
-      <c r="E116" s="0">
-        <v>2</v>
-      </c>
-      <c r="F116" s="0" t="inlineStr">
+      <c r="F116" s="0">
+        <v>2</v>
+      </c>
+      <c r="G116" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G116" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H116" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J116" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K116" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4063,24 +4137,24 @@
       <c r="D117" s="0">
         <v>25</v>
       </c>
-      <c r="E117" s="0">
-        <v>1</v>
-      </c>
-      <c r="F117" s="0" t="inlineStr">
+      <c r="F117" s="0">
+        <v>1</v>
+      </c>
+      <c r="G117" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G117" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H117" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J117" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K117" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4099,24 +4173,24 @@
       <c r="D118" s="0">
         <v>25</v>
       </c>
-      <c r="E118" s="0">
-        <v>2</v>
-      </c>
-      <c r="F118" s="0" t="inlineStr">
+      <c r="F118" s="0">
+        <v>2</v>
+      </c>
+      <c r="G118" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G118" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H118" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J118" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K118" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4135,24 +4209,24 @@
       <c r="D119" s="0">
         <v>25</v>
       </c>
-      <c r="E119" s="0">
-        <v>1</v>
-      </c>
-      <c r="F119" s="0" t="inlineStr">
+      <c r="F119" s="0">
+        <v>1</v>
+      </c>
+      <c r="G119" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G119" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H119" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J119" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K119" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4171,24 +4245,24 @@
       <c r="D120" s="0">
         <v>25</v>
       </c>
-      <c r="E120" s="0">
-        <v>2</v>
-      </c>
-      <c r="F120" s="0" t="inlineStr">
+      <c r="F120" s="0">
+        <v>2</v>
+      </c>
+      <c r="G120" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G120" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H120" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J120" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K120" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4207,11 +4281,8 @@
       <c r="D121" s="0">
         <v>29</v>
       </c>
-      <c r="E121" s="0">
-        <v>1</v>
-      </c>
-      <c r="G121" s="0" t="b">
-        <v>0</v>
+      <c r="F121" s="0">
+        <v>1</v>
       </c>
       <c r="H121" s="0" t="b">
         <v>0</v>
@@ -4220,6 +4291,9 @@
         <v>0</v>
       </c>
       <c r="J121" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K121" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4238,24 +4312,24 @@
       <c r="D122" s="0">
         <v>29</v>
       </c>
-      <c r="E122" s="0">
-        <v>2</v>
-      </c>
-      <c r="F122" s="0" t="inlineStr">
+      <c r="F122" s="0">
+        <v>2</v>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G122" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H122" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J122" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K122" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4274,24 +4348,24 @@
       <c r="D123" s="0">
         <v>29</v>
       </c>
-      <c r="E123" s="0">
-        <v>1</v>
-      </c>
-      <c r="F123" s="0" t="inlineStr">
+      <c r="F123" s="0">
+        <v>1</v>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G123" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H123" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J123" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K123" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4310,24 +4384,24 @@
       <c r="D124" s="0">
         <v>29</v>
       </c>
-      <c r="E124" s="0">
-        <v>2</v>
-      </c>
-      <c r="F124" s="0" t="inlineStr">
+      <c r="F124" s="0">
+        <v>2</v>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G124" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H124" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J124" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K124" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4346,24 +4420,24 @@
       <c r="D125" s="0">
         <v>28</v>
       </c>
-      <c r="E125" s="0">
-        <v>1</v>
-      </c>
-      <c r="F125" s="0" t="inlineStr">
+      <c r="F125" s="0">
+        <v>1</v>
+      </c>
+      <c r="G125" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G125" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H125" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J125" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K125" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4382,17 +4456,14 @@
       <c r="D126" s="0">
         <v>28</v>
       </c>
-      <c r="E126" s="0">
-        <v>2</v>
-      </c>
-      <c r="F126" s="0" t="inlineStr">
+      <c r="F126" s="0">
+        <v>2</v>
+      </c>
+      <c r="G126" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G126" s="0" t="b">
-        <v>0</v>
-      </c>
       <c r="H126" s="0" t="b">
         <v>0</v>
       </c>
@@ -4400,6 +4471,9 @@
         <v>0</v>
       </c>
       <c r="J126" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K126" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4418,24 +4492,24 @@
       <c r="D127" s="0">
         <v>28</v>
       </c>
-      <c r="E127" s="0">
-        <v>1</v>
-      </c>
-      <c r="F127" s="0" t="inlineStr">
+      <c r="F127" s="0">
+        <v>1</v>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
-      <c r="G127" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H127" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J127" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K127" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4454,24 +4528,24 @@
       <c r="D128" s="0">
         <v>28</v>
       </c>
-      <c r="E128" s="0">
-        <v>2</v>
-      </c>
-      <c r="F128" s="0" t="inlineStr">
+      <c r="F128" s="0">
+        <v>2</v>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
-      <c r="G128" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H128" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J128" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K128" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4490,11 +4564,8 @@
       <c r="D129" s="0">
         <v>16</v>
       </c>
-      <c r="E129" s="0">
-        <v>1</v>
-      </c>
-      <c r="G129" s="0" t="b">
-        <v>0</v>
+      <c r="F129" s="0">
+        <v>1</v>
       </c>
       <c r="H129" s="0" t="b">
         <v>0</v>
@@ -4503,6 +4574,9 @@
         <v>0</v>
       </c>
       <c r="J129" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K129" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4521,11 +4595,8 @@
       <c r="D130" s="0">
         <v>16</v>
       </c>
-      <c r="E130" s="0">
-        <v>2</v>
-      </c>
-      <c r="G130" s="0" t="b">
-        <v>0</v>
+      <c r="F130" s="0">
+        <v>2</v>
       </c>
       <c r="H130" s="0" t="b">
         <v>0</v>
@@ -4534,6 +4605,9 @@
         <v>0</v>
       </c>
       <c r="J130" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K130" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4552,11 +4626,8 @@
       <c r="D131" s="0">
         <v>22</v>
       </c>
-      <c r="E131" s="0">
-        <v>2</v>
-      </c>
-      <c r="G131" s="0" t="b">
-        <v>0</v>
+      <c r="F131" s="0">
+        <v>2</v>
       </c>
       <c r="H131" s="0" t="b">
         <v>0</v>
@@ -4565,6 +4636,9 @@
         <v>0</v>
       </c>
       <c r="J131" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K131" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4583,12 +4657,9 @@
       <c r="D132" s="0">
         <v>1</v>
       </c>
-      <c r="E132" s="0">
+      <c r="F132" s="0">
         <v>4</v>
       </c>
-      <c r="G132" s="0" t="b">
-        <v>0</v>
-      </c>
       <c r="H132" s="0" t="b">
         <v>0</v>
       </c>
@@ -4596,6 +4667,9 @@
         <v>0</v>
       </c>
       <c r="J132" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K132" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4614,24 +4688,24 @@
       <c r="D133" s="0">
         <v>31</v>
       </c>
-      <c r="E133" s="0">
-        <v>1</v>
-      </c>
-      <c r="F133" s="0" t="inlineStr">
+      <c r="F133" s="0">
+        <v>1</v>
+      </c>
+      <c r="G133" s="0" t="inlineStr">
         <is>
           <t>New translator found spelling mistakes and said that this version has complex/formal words that are not suitable for laypersons across all of India</t>
         </is>
       </c>
-      <c r="G133" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H133" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J133" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K133" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4650,19 +4724,19 @@
       <c r="D134" s="0">
         <v>31</v>
       </c>
-      <c r="E134" s="0">
-        <v>1</v>
-      </c>
-      <c r="G134" s="0" t="b">
-        <v>0</v>
+      <c r="F134" s="0">
+        <v>1</v>
       </c>
       <c r="H134" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J134" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K134" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4681,19 +4755,19 @@
       <c r="D135" s="0">
         <v>31</v>
       </c>
-      <c r="E135" s="0">
-        <v>1</v>
-      </c>
-      <c r="G135" s="0" t="b">
-        <v>0</v>
+      <c r="F135" s="0">
+        <v>1</v>
       </c>
       <c r="H135" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K135" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4712,19 +4786,19 @@
       <c r="D136" s="0">
         <v>31</v>
       </c>
-      <c r="E136" s="0">
-        <v>1</v>
-      </c>
-      <c r="G136" s="0" t="b">
-        <v>0</v>
+      <c r="F136" s="0">
+        <v>1</v>
       </c>
       <c r="H136" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K136" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4743,19 +4817,19 @@
       <c r="D137" s="0">
         <v>31</v>
       </c>
-      <c r="E137" s="0">
-        <v>1</v>
-      </c>
-      <c r="G137" s="0" t="b">
-        <v>0</v>
+      <c r="F137" s="0">
+        <v>1</v>
       </c>
       <c r="H137" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K137" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4774,19 +4848,19 @@
       <c r="D138" s="0">
         <v>32</v>
       </c>
-      <c r="E138" s="0">
-        <v>1</v>
-      </c>
-      <c r="G138" s="0" t="b">
-        <v>0</v>
+      <c r="F138" s="0">
+        <v>1</v>
       </c>
       <c r="H138" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K138" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4805,19 +4879,19 @@
       <c r="D139" s="0">
         <v>32</v>
       </c>
-      <c r="E139" s="0">
-        <v>2</v>
-      </c>
-      <c r="G139" s="0" t="b">
-        <v>0</v>
+      <c r="F139" s="0">
+        <v>2</v>
       </c>
       <c r="H139" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K139" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4836,19 +4910,19 @@
       <c r="D140" s="0">
         <v>32</v>
       </c>
-      <c r="E140" s="0">
-        <v>1</v>
-      </c>
-      <c r="G140" s="0" t="b">
-        <v>0</v>
+      <c r="F140" s="0">
+        <v>1</v>
       </c>
       <c r="H140" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K140" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4867,19 +4941,19 @@
       <c r="D141" s="0">
         <v>32</v>
       </c>
-      <c r="E141" s="0">
-        <v>2</v>
-      </c>
-      <c r="G141" s="0" t="b">
-        <v>0</v>
+      <c r="F141" s="0">
+        <v>2</v>
       </c>
       <c r="H141" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K141" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4898,11 +4972,8 @@
       <c r="D142" s="0">
         <v>27</v>
       </c>
-      <c r="E142" s="0">
-        <v>1</v>
-      </c>
-      <c r="G142" s="0" t="b">
-        <v>0</v>
+      <c r="F142" s="0">
+        <v>1</v>
       </c>
       <c r="H142" s="0" t="b">
         <v>0</v>
@@ -4911,6 +4982,9 @@
         <v>0</v>
       </c>
       <c r="J142" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K142" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4929,11 +5003,8 @@
       <c r="D143" s="0">
         <v>27</v>
       </c>
-      <c r="E143" s="0">
-        <v>1</v>
-      </c>
-      <c r="G143" s="0" t="b">
-        <v>0</v>
+      <c r="F143" s="0">
+        <v>1</v>
       </c>
       <c r="H143" s="0" t="b">
         <v>0</v>
@@ -4942,6 +5013,9 @@
         <v>0</v>
       </c>
       <c r="J143" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K143" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4960,19 +5034,19 @@
       <c r="D144" s="0">
         <v>38</v>
       </c>
-      <c r="E144" s="0">
-        <v>1</v>
-      </c>
-      <c r="G144" s="0" t="b">
-        <v>0</v>
+      <c r="F144" s="0">
+        <v>1</v>
       </c>
       <c r="H144" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K144" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4991,24 +5065,24 @@
       <c r="D145" s="0">
         <v>8</v>
       </c>
-      <c r="E145" s="0">
-        <v>2</v>
-      </c>
-      <c r="F145" s="0" t="inlineStr">
-        <is>
-          <t>Dayer 2023</t>
-        </is>
-      </c>
-      <c r="G145" s="0" t="b">
-        <v>1</v>
+      <c r="F145" s="0">
+        <v>2</v>
+      </c>
+      <c r="G145" s="0" t="inlineStr">
+        <is>
+          <t>Dayer 2023 - unknown if canadian or france french- google team?</t>
+        </is>
       </c>
       <c r="H145" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J145" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K145" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5027,24 +5101,24 @@
       <c r="D146" s="0">
         <v>8</v>
       </c>
-      <c r="E146" s="0">
-        <v>2</v>
-      </c>
-      <c r="F146" s="0" t="inlineStr">
+      <c r="F146" s="0">
+        <v>2</v>
+      </c>
+      <c r="G146" s="0" t="inlineStr">
         <is>
           <t>Unauthorized version from NHS (UK)</t>
         </is>
       </c>
-      <c r="G146" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H146" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I146" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J146" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K146" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5063,24 +5137,24 @@
       <c r="D147" s="0">
         <v>8</v>
       </c>
-      <c r="E147" s="0">
-        <v>1</v>
-      </c>
-      <c r="F147" s="0" t="inlineStr">
+      <c r="F147" s="0">
+        <v>1</v>
+      </c>
+      <c r="G147" s="0" t="inlineStr">
         <is>
           <t>Boustani update</t>
         </is>
       </c>
-      <c r="G147" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H147" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J147" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K147" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5099,19 +5173,19 @@
       <c r="D148" s="0">
         <v>38</v>
       </c>
-      <c r="E148" s="0">
-        <v>2</v>
-      </c>
-      <c r="G148" s="0" t="b">
-        <v>0</v>
+      <c r="F148" s="0">
+        <v>2</v>
       </c>
       <c r="H148" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K148" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5130,19 +5204,19 @@
       <c r="D149" s="0">
         <v>38</v>
       </c>
-      <c r="E149" s="0">
-        <v>1</v>
-      </c>
-      <c r="G149" s="0" t="b">
-        <v>0</v>
+      <c r="F149" s="0">
+        <v>1</v>
       </c>
       <c r="H149" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K149" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5161,19 +5235,19 @@
       <c r="D150" s="0">
         <v>38</v>
       </c>
-      <c r="E150" s="0">
-        <v>2</v>
-      </c>
-      <c r="G150" s="0" t="b">
-        <v>0</v>
+      <c r="F150" s="0">
+        <v>2</v>
       </c>
       <c r="H150" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K150" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5190,26 +5264,29 @@
         <v>1</v>
       </c>
       <c r="D151" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E151" s="0">
-        <v>1</v>
-      </c>
-      <c r="F151" s="0" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F151" s="0">
+        <v>1</v>
+      </c>
+      <c r="G151" s="0" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G151" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H151" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J151" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K151" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5219,7 +5296,7 @@
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>RCADS-47-CG-FR-3</t>
+          <t>RCADS-47-CG-FR-FR-3</t>
         </is>
       </c>
       <c r="C152" s="0">
@@ -5229,23 +5306,26 @@
         <v>8</v>
       </c>
       <c r="E152" s="0">
-        <v>2</v>
-      </c>
-      <c r="F152" s="0" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="F152" s="0">
+        <v>2</v>
+      </c>
+      <c r="G152" s="0" t="inlineStr">
         <is>
           <t>Boustani update, combined versions 1 and 2 while consulting youth version 1</t>
         </is>
       </c>
-      <c r="G152" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H152" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J152" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K152" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5262,26 +5342,29 @@
         <v>1</v>
       </c>
       <c r="D153" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E153" s="0">
-        <v>1</v>
-      </c>
-      <c r="F153" s="0" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F153" s="0">
+        <v>1</v>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
         <is>
           <t>No items; Unauthorized Canadian changes</t>
         </is>
       </c>
-      <c r="G153" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H153" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J153" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K153" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5298,26 +5381,29 @@
         <v>1</v>
       </c>
       <c r="D154" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E154" s="0">
-        <v>2</v>
-      </c>
-      <c r="F154" s="0" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="F154" s="0">
+        <v>2</v>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G154" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H154" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J154" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K154" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5336,11 +5422,8 @@
       <c r="D155" s="0">
         <v>36</v>
       </c>
-      <c r="E155" s="0">
-        <v>1</v>
-      </c>
-      <c r="G155" s="0" t="b">
-        <v>0</v>
+      <c r="F155" s="0">
+        <v>1</v>
       </c>
       <c r="H155" s="0" t="b">
         <v>0</v>
@@ -5349,6 +5432,9 @@
         <v>0</v>
       </c>
       <c r="J155" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K155" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5367,11 +5453,8 @@
       <c r="D156" s="0">
         <v>36</v>
       </c>
-      <c r="E156" s="0">
-        <v>2</v>
-      </c>
-      <c r="G156" s="0" t="b">
-        <v>0</v>
+      <c r="F156" s="0">
+        <v>2</v>
       </c>
       <c r="H156" s="0" t="b">
         <v>0</v>
@@ -5380,6 +5463,9 @@
         <v>0</v>
       </c>
       <c r="J156" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K156" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5398,19 +5484,19 @@
       <c r="D157" s="0">
         <v>1</v>
       </c>
-      <c r="E157" s="0">
-        <v>2</v>
-      </c>
-      <c r="G157" s="0" t="b">
-        <v>0</v>
+      <c r="F157" s="0">
+        <v>2</v>
       </c>
       <c r="H157" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I157" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K157" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5429,19 +5515,19 @@
       <c r="D158" s="0">
         <v>1</v>
       </c>
-      <c r="E158" s="0">
-        <v>2</v>
-      </c>
-      <c r="G158" s="0" t="b">
-        <v>0</v>
+      <c r="F158" s="0">
+        <v>2</v>
       </c>
       <c r="H158" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K158" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5460,19 +5546,19 @@
       <c r="D159" s="0">
         <v>34</v>
       </c>
-      <c r="E159" s="0">
-        <v>1</v>
-      </c>
-      <c r="G159" s="0" t="b">
-        <v>0</v>
+      <c r="F159" s="0">
+        <v>1</v>
       </c>
       <c r="H159" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K159" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5491,19 +5577,19 @@
       <c r="D160" s="0">
         <v>34</v>
       </c>
-      <c r="E160" s="0">
-        <v>2</v>
-      </c>
-      <c r="G160" s="0" t="b">
-        <v>0</v>
+      <c r="F160" s="0">
+        <v>2</v>
       </c>
       <c r="H160" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K160" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5522,24 +5608,24 @@
       <c r="D161" s="0">
         <v>34</v>
       </c>
-      <c r="E161" s="0">
-        <v>1</v>
-      </c>
-      <c r="F161" s="0" t="inlineStr">
+      <c r="F161" s="0">
+        <v>1</v>
+      </c>
+      <c r="G161" s="0" t="inlineStr">
         <is>
           <t>Inconsistent codebook response option</t>
         </is>
       </c>
-      <c r="G161" s="0" t="b">
-        <v>1</v>
-      </c>
       <c r="H161" s="0" t="b">
         <v>1</v>
       </c>
       <c r="I161" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K161" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5558,19 +5644,19 @@
       <c r="D162" s="0">
         <v>34</v>
       </c>
-      <c r="E162" s="0">
-        <v>2</v>
-      </c>
-      <c r="G162" s="0" t="b">
-        <v>0</v>
+      <c r="F162" s="0">
+        <v>2</v>
       </c>
       <c r="H162" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K162" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5589,19 +5675,19 @@
       <c r="D163" s="0">
         <v>39</v>
       </c>
-      <c r="E163" s="0">
-        <v>1</v>
-      </c>
-      <c r="G163" s="0" t="b">
-        <v>0</v>
+      <c r="F163" s="0">
+        <v>1</v>
       </c>
       <c r="H163" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K163" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5620,19 +5706,19 @@
       <c r="D164" s="0">
         <v>39</v>
       </c>
-      <c r="E164" s="0">
-        <v>2</v>
-      </c>
-      <c r="G164" s="0" t="b">
-        <v>0</v>
+      <c r="F164" s="0">
+        <v>2</v>
       </c>
       <c r="H164" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K164" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5651,19 +5737,19 @@
       <c r="D165" s="0">
         <v>39</v>
       </c>
-      <c r="E165" s="0">
-        <v>1</v>
-      </c>
-      <c r="G165" s="0" t="b">
-        <v>0</v>
+      <c r="F165" s="0">
+        <v>1</v>
       </c>
       <c r="H165" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K165" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5682,19 +5768,19 @@
       <c r="D166" s="0">
         <v>39</v>
       </c>
-      <c r="E166" s="0">
-        <v>2</v>
-      </c>
-      <c r="G166" s="0" t="b">
-        <v>0</v>
+      <c r="F166" s="0">
+        <v>2</v>
       </c>
       <c r="H166" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K166" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5713,19 +5799,19 @@
       <c r="D167" s="0">
         <v>40</v>
       </c>
-      <c r="E167" s="0">
-        <v>1</v>
-      </c>
-      <c r="G167" s="0" t="b">
-        <v>0</v>
+      <c r="F167" s="0">
+        <v>1</v>
       </c>
       <c r="H167" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K167" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5744,19 +5830,19 @@
       <c r="D168" s="0">
         <v>40</v>
       </c>
-      <c r="E168" s="0">
-        <v>2</v>
-      </c>
-      <c r="G168" s="0" t="b">
-        <v>0</v>
+      <c r="F168" s="0">
+        <v>2</v>
       </c>
       <c r="H168" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K168" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5775,19 +5861,19 @@
       <c r="D169" s="0">
         <v>40</v>
       </c>
-      <c r="E169" s="0">
-        <v>1</v>
-      </c>
-      <c r="G169" s="0" t="b">
-        <v>0</v>
+      <c r="F169" s="0">
+        <v>1</v>
       </c>
       <c r="H169" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K169" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5806,19 +5892,19 @@
       <c r="D170" s="0">
         <v>40</v>
       </c>
-      <c r="E170" s="0">
-        <v>2</v>
-      </c>
-      <c r="G170" s="0" t="b">
-        <v>0</v>
+      <c r="F170" s="0">
+        <v>2</v>
       </c>
       <c r="H170" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K170" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5837,11 +5923,8 @@
       <c r="D171" s="0">
         <v>36</v>
       </c>
-      <c r="E171" s="0">
-        <v>1</v>
-      </c>
-      <c r="G171" s="0" t="b">
-        <v>0</v>
+      <c r="F171" s="0">
+        <v>1</v>
       </c>
       <c r="H171" s="0" t="b">
         <v>0</v>
@@ -5850,6 +5933,9 @@
         <v>0</v>
       </c>
       <c r="J171" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K171" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5868,11 +5954,8 @@
       <c r="D172" s="0">
         <v>36</v>
       </c>
-      <c r="E172" s="0">
-        <v>2</v>
-      </c>
-      <c r="G172" s="0" t="b">
-        <v>0</v>
+      <c r="F172" s="0">
+        <v>2</v>
       </c>
       <c r="H172" s="0" t="b">
         <v>0</v>
@@ -5881,6 +5964,9 @@
         <v>0</v>
       </c>
       <c r="J172" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K172" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5899,19 +5985,19 @@
       <c r="D173" s="0">
         <v>41</v>
       </c>
-      <c r="E173" s="0">
-        <v>1</v>
-      </c>
-      <c r="G173" s="0" t="b">
-        <v>0</v>
+      <c r="F173" s="0">
+        <v>1</v>
       </c>
       <c r="H173" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J173" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K173" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5930,19 +6016,19 @@
       <c r="D174" s="0">
         <v>41</v>
       </c>
-      <c r="E174" s="0">
-        <v>2</v>
-      </c>
-      <c r="G174" s="0" t="b">
-        <v>0</v>
+      <c r="F174" s="0">
+        <v>2</v>
       </c>
       <c r="H174" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J174" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K174" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5961,19 +6047,19 @@
       <c r="D175" s="0">
         <v>41</v>
       </c>
-      <c r="E175" s="0">
-        <v>1</v>
-      </c>
-      <c r="G175" s="0" t="b">
-        <v>0</v>
+      <c r="F175" s="0">
+        <v>1</v>
       </c>
       <c r="H175" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K175" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5992,19 +6078,19 @@
       <c r="D176" s="0">
         <v>41</v>
       </c>
-      <c r="E176" s="0">
-        <v>2</v>
-      </c>
-      <c r="G176" s="0" t="b">
-        <v>0</v>
+      <c r="F176" s="0">
+        <v>2</v>
       </c>
       <c r="H176" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J176" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K176" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6023,19 +6109,412 @@
       <c r="D177" s="0">
         <v>34</v>
       </c>
-      <c r="E177" s="0">
-        <v>1</v>
-      </c>
-      <c r="G177" s="0" t="b">
-        <v>0</v>
+      <c r="F177" s="0">
+        <v>1</v>
       </c>
       <c r="H177" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K177" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="178">
+      <c r="A178" s="0">
+        <v>177</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-Y-SQ</t>
+        </is>
+      </c>
+      <c r="C178" s="0">
+        <v>1</v>
+      </c>
+      <c r="D178" s="0">
+        <v>42</v>
+      </c>
+      <c r="F178" s="0">
+        <v>1</v>
+      </c>
+      <c r="H178" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I178" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J178" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K178" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="179">
+      <c r="A179" s="0">
+        <v>178</v>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-CG-SQ</t>
+        </is>
+      </c>
+      <c r="C179" s="0">
+        <v>1</v>
+      </c>
+      <c r="D179" s="0">
+        <v>42</v>
+      </c>
+      <c r="F179" s="0">
+        <v>2</v>
+      </c>
+      <c r="H179" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J179" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K179" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="180">
+      <c r="A180" s="0">
+        <v>179</v>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-SQ</t>
+        </is>
+      </c>
+      <c r="C180" s="0">
+        <v>1</v>
+      </c>
+      <c r="D180" s="0">
+        <v>42</v>
+      </c>
+      <c r="F180" s="0">
+        <v>1</v>
+      </c>
+      <c r="H180" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I180" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J180" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K180" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="181">
+      <c r="A181" s="0">
+        <v>180</v>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-SQ</t>
+        </is>
+      </c>
+      <c r="C181" s="0">
+        <v>1</v>
+      </c>
+      <c r="D181" s="0">
+        <v>42</v>
+      </c>
+      <c r="F181" s="0">
+        <v>2</v>
+      </c>
+      <c r="H181" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J181" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K181" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="182">
+      <c r="A182" s="0">
+        <v>181</v>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-9-A-EN-US</t>
+        </is>
+      </c>
+      <c r="C182" s="0">
+        <v>4</v>
+      </c>
+      <c r="D182" s="0">
+        <v>1</v>
+      </c>
+      <c r="E182" s="0">
+        <v>1</v>
+      </c>
+      <c r="F182" s="0">
+        <v>4</v>
+      </c>
+      <c r="H182" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I182" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J182" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K182" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="183">
+      <c r="A183" s="0">
+        <v>182</v>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-8-A-EN-UK</t>
+        </is>
+      </c>
+      <c r="C183" s="0">
+        <v>4</v>
+      </c>
+      <c r="D183" s="0">
+        <v>1</v>
+      </c>
+      <c r="E183" s="0">
+        <v>9</v>
+      </c>
+      <c r="F183" s="0">
+        <v>4</v>
+      </c>
+      <c r="H183" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I183" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J183" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K183" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="184">
+      <c r="A184" s="0">
+        <v>183</v>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-8-A-EN-CA</t>
+        </is>
+      </c>
+      <c r="C184" s="0">
+        <v>4</v>
+      </c>
+      <c r="D184" s="0">
+        <v>1</v>
+      </c>
+      <c r="E184" s="0">
+        <v>8</v>
+      </c>
+      <c r="F184" s="0">
+        <v>4</v>
+      </c>
+      <c r="H184" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I184" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J184" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K184" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="185">
+      <c r="A185" s="0">
+        <v>184</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-8-A-EN-AU</t>
+        </is>
+      </c>
+      <c r="C185" s="0">
+        <v>4</v>
+      </c>
+      <c r="D185" s="0">
+        <v>1</v>
+      </c>
+      <c r="E185" s="0">
+        <v>10</v>
+      </c>
+      <c r="F185" s="0">
+        <v>4</v>
+      </c>
+      <c r="H185" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I185" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J185" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K185" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="186">
+      <c r="A186" s="0">
+        <v>185</v>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-9-A-EN-AU</t>
+        </is>
+      </c>
+      <c r="C186" s="0">
+        <v>4</v>
+      </c>
+      <c r="D186" s="0">
+        <v>1</v>
+      </c>
+      <c r="E186" s="0">
+        <v>10</v>
+      </c>
+      <c r="F186" s="0">
+        <v>4</v>
+      </c>
+      <c r="H186" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I186" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J186" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K186" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="187">
+      <c r="A187" s="0">
+        <v>186</v>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-9-A-EN-HK</t>
+        </is>
+      </c>
+      <c r="C187" s="0">
+        <v>4</v>
+      </c>
+      <c r="D187" s="0">
+        <v>1</v>
+      </c>
+      <c r="E187" s="0">
+        <v>11</v>
+      </c>
+      <c r="F187" s="0">
+        <v>4</v>
+      </c>
+      <c r="H187" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I187" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J187" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K187" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="188">
+      <c r="A188" s="0">
+        <v>187</v>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-4-A-EN</t>
+        </is>
+      </c>
+      <c r="C188" s="0">
+        <v>4</v>
+      </c>
+      <c r="D188" s="0">
+        <v>1</v>
+      </c>
+      <c r="F188" s="0">
+        <v>4</v>
+      </c>
+      <c r="H188" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I188" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J188" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K188" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="189">
+      <c r="A189" s="0">
+        <v>188</v>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-9-A-FR-FR</t>
+        </is>
+      </c>
+      <c r="C189" s="0">
+        <v>4</v>
+      </c>
+      <c r="D189" s="0">
+        <v>1</v>
+      </c>
+      <c r="E189" s="0">
+        <v>4</v>
+      </c>
+      <c r="F189" s="0">
+        <v>4</v>
+      </c>
+      <c r="H189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K189" s="0" t="b">
         <v>0</v>
       </c>
     </row>
